--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-parameters-out-plan-read.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
